--- a/Result/profitability/1472.xlsx
+++ b/Result/profitability/1472.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>1.20625</v>
+        <v>1.35375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.99625</v>
+        <v>11.1675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.68</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0575</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>8.88875</v>
+        <v>9.40875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.82875</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>7.305</v>
+        <v>7.0725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.82</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5062500000000001</v>
+        <v>0.5025000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>3.54375</v>
+        <v>3.3625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1887500000000001</v>
+        <v>0.1975000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1225</v>
+        <v>-1.09875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08874999999999994</v>
+        <v>-0.03999999999999995</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.635</v>
+        <v>-5.2775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.345</v>
+        <v>-0.35625</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.3675</v>
+        <v>-8.446249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.54375</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.6975</v>
+        <v>-7.697500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>996</v>
+      </c>
+      <c r="D75" t="n">
+        <v>856</v>
+      </c>
+      <c r="E75" t="n">
+        <v>140</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>106</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>108</v>
+      </c>
+      <c r="K75" t="n">
+        <v>89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.48625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09000000000000008</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.050561797752809</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6300000000000008</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0429447852760737</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.01744186046511631</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.450000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.093608779857973</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
